--- a/results/categories_3_months.xlsx
+++ b/results/categories_3_months.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,16 +507,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04.10.2021 13:03:58</t>
+          <t>29.09.2021 16:40:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>04.03.2021</t>
+          <t>29.09.2021</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-99</v>
+        <v>-110</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-99</v>
+        <v>-110</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -558,26 +558,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Mouse Tail</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>04.10.2021 12:41:29</t>
+          <t>04.10.2021 13:03:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-56</v>
+        <v>-99</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-56</v>
+        <v>-99</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Rumyanyj Khleb</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -634,7 +634,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4">
@@ -643,12 +643,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>03.10.2021 14:30:11</t>
+          <t>04.10.2021 12:41:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>03.03.2021</t>
+          <t>04.03.2021</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-99</v>
+        <v>-56</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-99</v>
+        <v>-56</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Rumyanyj Khleb</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>99</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
@@ -709,7 +709,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>03.10.2021 12:39:09</t>
+          <t>03.10.2021 14:30:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>*5684</t>
+          <t>*7197</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -766,6 +766,72 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>03.10.2021 12:39:09</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>03.03.2021</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>*5684</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>-99</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>-99</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>5814</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>McDonald's</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>99</v>
       </c>
     </row>
